--- a/data/3.meta_data/matrices/0107a.xlsx
+++ b/data/3.meta_data/matrices/0107a.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -430,709 +430,1269 @@
           <t>openness</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>perspectivetakingskill</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>capacityfortrust</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>capacityforsocialwarmth</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>teamworkskill</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ethicalcompetence</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>-0.06150886251175378</v>
+        <v>-0.05095158978178231</v>
       </c>
       <c r="C2">
-        <v>0.07860095872083388</v>
+        <v>0.06893275010365721</v>
       </c>
       <c r="D2">
-        <v>0.2159801016294211</v>
+        <v>0.2139629103042538</v>
       </c>
       <c r="E2">
-        <v>0.04515939810525333</v>
+        <v>0.04387883041485736</v>
       </c>
       <c r="F2">
-        <v>0.1284551420396477</v>
+        <v>0.1351859546757259</v>
       </c>
       <c r="G2">
-        <v>-0.08315263555962156</v>
+        <v>-0.0817608833535739</v>
       </c>
       <c r="H2">
-        <v>0.08424703962134236</v>
+        <v>0.09305279398789197</v>
       </c>
       <c r="I2">
-        <v>0.1678306454838297</v>
+        <v>0.1491285742838097</v>
       </c>
       <c r="J2">
-        <v>0.2054810311219833</v>
+        <v>0.2227186264875546</v>
       </c>
       <c r="K2">
-        <v>-0.192922253287266</v>
+        <v>-0.2032438124394959</v>
       </c>
       <c r="L2">
-        <v>0.1635289584750014</v>
+        <v>0.1703700458011537</v>
       </c>
       <c r="M2">
-        <v>0.2462195022844721</v>
+        <v>0.2510782525818244</v>
       </c>
       <c r="N2">
-        <v>0.06776122405072027</v>
+        <v>0.04459276354807663</v>
       </c>
       <c r="O2">
-        <v>-0.1278059168004523</v>
+        <v>-0.1404150485086712</v>
+      </c>
+      <c r="P2">
+        <v>0.1498514333392476</v>
+      </c>
+      <c r="Q2">
+        <v>0.07726138752518816</v>
+      </c>
+      <c r="R2">
+        <v>0.1144527085473046</v>
+      </c>
+      <c r="S2">
+        <v>0.2637355905648565</v>
+      </c>
+      <c r="T2">
+        <v>0.2538913410223593</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>-0.06150886251175378</v>
+        <v>-0.05095158978178231</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>0.06451155993190349</v>
+        <v>0.05763490836987898</v>
       </c>
       <c r="D3">
-        <v>0.02372651823087872</v>
+        <v>0.02199088141941908</v>
       </c>
       <c r="E3">
-        <v>0.1328640964946553</v>
+        <v>0.1319736391050337</v>
       </c>
       <c r="F3">
-        <v>0.1038331378484232</v>
+        <v>0.1101910516364609</v>
       </c>
       <c r="G3">
-        <v>0.004085512236148251</v>
+        <v>0.00466894858974371</v>
       </c>
       <c r="H3">
-        <v>0.2205086237293833</v>
+        <v>0.2259395559494152</v>
       </c>
       <c r="I3">
-        <v>-0.2364956450038418</v>
+        <v>-0.2449972605778508</v>
       </c>
       <c r="J3">
-        <v>0.1601874074349052</v>
+        <v>0.1732248620886273</v>
       </c>
       <c r="K3">
-        <v>0.2200661426643098</v>
+        <v>0.2085662646529877</v>
       </c>
       <c r="L3">
-        <v>-0.01436676818842181</v>
+        <v>-0.009559106541230319</v>
       </c>
       <c r="M3">
-        <v>-0.03598643687849504</v>
+        <v>-0.03070042189020344</v>
       </c>
       <c r="N3">
-        <v>-0.1873545299721046</v>
+        <v>-0.199454559182896</v>
       </c>
       <c r="O3">
-        <v>0.2605993605348391</v>
+        <v>0.2464520058367095</v>
+      </c>
+      <c r="P3">
+        <v>0.1085776736285352</v>
+      </c>
+      <c r="Q3">
+        <v>0.2028890976282736</v>
+      </c>
+      <c r="R3">
+        <v>0.1367630776388218</v>
+      </c>
+      <c r="S3">
+        <v>0.05484384196750863</v>
+      </c>
+      <c r="T3">
+        <v>0.1124389432384647</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.07860095872083388</v>
+        <v>0.06893275010365721</v>
       </c>
       <c r="B4">
-        <v>0.06451155993190349</v>
+        <v>0.05763490836987898</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>0.2507620237969958</v>
+        <v>0.2493824650670426</v>
       </c>
       <c r="E4">
-        <v>-0.004005902624904399</v>
+        <v>-0.003329074654288966</v>
       </c>
       <c r="F4">
-        <v>0.06765215920580638</v>
+        <v>0.06199503924089891</v>
       </c>
       <c r="G4">
-        <v>-0.1067004645889708</v>
+        <v>-0.1069249440622759</v>
       </c>
       <c r="H4">
-        <v>0.06528899280977216</v>
+        <v>0.05853909847704408</v>
       </c>
       <c r="I4">
-        <v>0.1664641305650976</v>
+        <v>0.1748824064642598</v>
       </c>
       <c r="J4">
-        <v>0.1005480868004269</v>
+        <v>0.08365565873081771</v>
       </c>
       <c r="K4">
-        <v>0.104015465035635</v>
+        <v>0.1114677623722407</v>
       </c>
       <c r="L4">
-        <v>0.1254570167154984</v>
+        <v>0.1182614533242573</v>
       </c>
       <c r="M4">
-        <v>0.06607312685521408</v>
+        <v>0.06119142843282951</v>
       </c>
       <c r="N4">
-        <v>0.07996995828609169</v>
+        <v>0.09243126180872226</v>
       </c>
       <c r="O4">
-        <v>0.0381212233398639</v>
+        <v>0.04715800174151601</v>
+      </c>
+      <c r="P4">
+        <v>-0.04094400070885888</v>
+      </c>
+      <c r="Q4">
+        <v>0.02203706588251925</v>
+      </c>
+      <c r="R4">
+        <v>0.09100976823142341</v>
+      </c>
+      <c r="S4">
+        <v>0.1689101999126812</v>
+      </c>
+      <c r="T4">
+        <v>0.09047973358408784</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.2159801016294211</v>
+        <v>0.2139629103042538</v>
       </c>
       <c r="B5">
-        <v>0.02372651823087872</v>
+        <v>0.02199088141941908</v>
       </c>
       <c r="C5">
-        <v>0.2507620237969958</v>
+        <v>0.2493824650670426</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>-0.06847517969882143</v>
+        <v>-0.06930902017251134</v>
       </c>
       <c r="F5">
-        <v>0.1316992551065261</v>
+        <v>0.1272379017970055</v>
       </c>
       <c r="G5">
-        <v>-0.2786073361372114</v>
+        <v>-0.2779884681927899</v>
       </c>
       <c r="H5">
-        <v>0.1748333252865522</v>
+        <v>0.17379571712786</v>
       </c>
       <c r="I5">
-        <v>0.226973298262108</v>
+        <v>0.2244150345830125</v>
       </c>
       <c r="J5">
-        <v>0.2814636725025564</v>
+        <v>0.2746088583062065</v>
       </c>
       <c r="K5">
-        <v>0.07951076396055393</v>
+        <v>0.07892171432252326</v>
       </c>
       <c r="L5">
-        <v>0.1972983585352703</v>
+        <v>0.200958966353168</v>
       </c>
       <c r="M5">
-        <v>0.1556907547687171</v>
+        <v>0.1550320234728836</v>
       </c>
       <c r="N5">
-        <v>0.08808353091238505</v>
+        <v>0.08754628572900472</v>
       </c>
       <c r="O5">
-        <v>0.1086231381843897</v>
+        <v>0.109024750750756</v>
+      </c>
+      <c r="P5">
+        <v>0.1650741730086829</v>
+      </c>
+      <c r="Q5">
+        <v>0.1505053023167987</v>
+      </c>
+      <c r="R5">
+        <v>0.1742055213462483</v>
+      </c>
+      <c r="S5">
+        <v>0.3161345848856572</v>
+      </c>
+      <c r="T5">
+        <v>0.198409316562796</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04515939810525333</v>
+        <v>0.04387883041485736</v>
       </c>
       <c r="B6">
-        <v>0.1328640964946553</v>
+        <v>0.1319736391050337</v>
       </c>
       <c r="C6">
-        <v>-0.004005902624904399</v>
+        <v>-0.003329074654288966</v>
       </c>
       <c r="D6">
-        <v>-0.06847517969882143</v>
+        <v>-0.06930902017251134</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>-0.008731506082484141</v>
+        <v>-0.008453684698404499</v>
       </c>
       <c r="G6">
-        <v>0.1986784451845265</v>
+        <v>0.1985856879700938</v>
       </c>
       <c r="H6">
-        <v>0.008706306614640983</v>
+        <v>0.007987745837950528</v>
       </c>
       <c r="I6">
-        <v>-0.034374954096852</v>
+        <v>-0.03290908989607596</v>
       </c>
       <c r="J6">
-        <v>-0.1131078795232538</v>
+        <v>-0.1123713039747314</v>
       </c>
       <c r="K6">
-        <v>0.08322271371806197</v>
+        <v>0.08361725227997958</v>
       </c>
       <c r="L6">
-        <v>-0.2609841784803624</v>
+        <v>-0.2611696373840359</v>
       </c>
       <c r="M6">
-        <v>0.06983794450422055</v>
+        <v>0.06920663782528157</v>
       </c>
       <c r="N6">
-        <v>0.0005645537134997134</v>
+        <v>0.001843250891151417</v>
       </c>
       <c r="O6">
-        <v>0.01551564781335734</v>
+        <v>0.01609515334306257</v>
+      </c>
+      <c r="P6">
+        <v>-0.1055307157996861</v>
+      </c>
+      <c r="Q6">
+        <v>-0.2589518106208061</v>
+      </c>
+      <c r="R6">
+        <v>0.008152773604969592</v>
+      </c>
+      <c r="S6">
+        <v>-0.003206281458413307</v>
+      </c>
+      <c r="T6">
+        <v>0.02970359868433875</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.1284551420396477</v>
+        <v>0.1351859546757259</v>
       </c>
       <c r="B7">
-        <v>0.1038331378484232</v>
+        <v>0.1101910516364609</v>
       </c>
       <c r="C7">
-        <v>0.06765215920580638</v>
+        <v>0.06199503924089891</v>
       </c>
       <c r="D7">
-        <v>0.1316992551065261</v>
+        <v>0.1272379017970055</v>
       </c>
       <c r="E7">
-        <v>-0.008731506082484141</v>
+        <v>-0.008453684698404499</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>-0.07020984704818885</v>
+        <v>-0.06944337897813582</v>
       </c>
       <c r="H7">
-        <v>0.106643952250876</v>
+        <v>0.111627694341269</v>
       </c>
       <c r="I7">
-        <v>0.07706042505883423</v>
+        <v>0.06650251466758206</v>
       </c>
       <c r="J7">
-        <v>0.289818636903774</v>
+        <v>0.2973247065830599</v>
       </c>
       <c r="K7">
-        <v>0.1236167160637273</v>
+        <v>0.1147600560033856</v>
       </c>
       <c r="L7">
-        <v>0.1915668870945708</v>
+        <v>0.1905800200173855</v>
       </c>
       <c r="M7">
-        <v>-0.01490985285469092</v>
+        <v>-0.01066490304663156</v>
       </c>
       <c r="N7">
-        <v>-0.06684242044665795</v>
+        <v>-0.07914808429291659</v>
       </c>
       <c r="O7">
-        <v>0.05961009914521846</v>
+        <v>0.04908496577092072</v>
+      </c>
+      <c r="P7">
+        <v>0.07933358605274295</v>
+      </c>
+      <c r="Q7">
+        <v>0.4873320020387907</v>
+      </c>
+      <c r="R7">
+        <v>0.2129724037674157</v>
+      </c>
+      <c r="S7">
+        <v>0.1375954870889755</v>
+      </c>
+      <c r="T7">
+        <v>0.07858683641614395</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>-0.08315263555962156</v>
+        <v>-0.0817608833535739</v>
       </c>
       <c r="B8">
-        <v>0.004085512236148251</v>
+        <v>0.00466894858974371</v>
       </c>
       <c r="C8">
-        <v>-0.1067004645889708</v>
+        <v>-0.1069249440622759</v>
       </c>
       <c r="D8">
-        <v>-0.2786073361372114</v>
+        <v>-0.2779884681927899</v>
       </c>
       <c r="E8">
-        <v>0.1986784451845265</v>
+        <v>0.1985856879700938</v>
       </c>
       <c r="F8">
-        <v>-0.07020984704818885</v>
+        <v>-0.06944337897813582</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>0.07788209036901049</v>
+        <v>0.07819717450390941</v>
       </c>
       <c r="I8">
-        <v>-0.1344548623094484</v>
+        <v>-0.1341494101292557</v>
       </c>
       <c r="J8">
-        <v>-0.06598409415717404</v>
+        <v>-0.06337668668375511</v>
       </c>
       <c r="K8">
-        <v>-0.06684782481868229</v>
+        <v>-0.06721692931158098</v>
       </c>
       <c r="L8">
-        <v>-0.08937910091710877</v>
+        <v>-0.08827536701546351</v>
       </c>
       <c r="M8">
-        <v>-0.08907985414498863</v>
+        <v>-0.08849569695377277</v>
       </c>
       <c r="N8">
-        <v>-0.05106108334772153</v>
+        <v>-0.05147795912522143</v>
       </c>
       <c r="O8">
-        <v>-0.1290678786495238</v>
+        <v>-0.1289103385701811</v>
+      </c>
+      <c r="P8">
+        <v>0.04178203312533061</v>
+      </c>
+      <c r="Q8">
+        <v>-0.08782373275430254</v>
+      </c>
+      <c r="R8">
+        <v>0.004570821820959719</v>
+      </c>
+      <c r="S8">
+        <v>-0.1043179236807127</v>
+      </c>
+      <c r="T8">
+        <v>-0.1225439494279437</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.08424703962134236</v>
+        <v>0.09305279398789197</v>
       </c>
       <c r="B9">
-        <v>0.2205086237293833</v>
+        <v>0.2259395559494152</v>
       </c>
       <c r="C9">
-        <v>0.06528899280977216</v>
+        <v>0.05853909847704408</v>
       </c>
       <c r="D9">
-        <v>0.1748333252865522</v>
+        <v>0.17379571712786</v>
       </c>
       <c r="E9">
-        <v>0.008706306614640983</v>
+        <v>0.007987745837950528</v>
       </c>
       <c r="F9">
-        <v>0.106643952250876</v>
+        <v>0.111627694341269</v>
       </c>
       <c r="G9">
-        <v>0.07788209036901049</v>
+        <v>0.07819717450390941</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9">
-        <v>-0.05523225291946129</v>
+        <v>-0.0658935659282681</v>
       </c>
       <c r="J9">
-        <v>0.1368641045250882</v>
+        <v>0.1498188364147499</v>
       </c>
       <c r="K9">
-        <v>0.05838872468510031</v>
+        <v>0.04873352411747953</v>
       </c>
       <c r="L9">
-        <v>0.04622065974247986</v>
+        <v>0.05215584806950567</v>
       </c>
       <c r="M9">
-        <v>0.1048961927547674</v>
+        <v>0.1093103177022212</v>
       </c>
       <c r="N9">
-        <v>-0.05160104124978684</v>
+        <v>-0.06585482154983935</v>
       </c>
       <c r="O9">
-        <v>-0.001419502472943161</v>
+        <v>-0.01171596336165348</v>
+      </c>
+      <c r="P9">
+        <v>0.07317528681095627</v>
+      </c>
+      <c r="Q9">
+        <v>0.1158528245081843</v>
+      </c>
+      <c r="R9">
+        <v>0.137555541604289</v>
+      </c>
+      <c r="S9">
+        <v>0.1260738839238227</v>
+      </c>
+      <c r="T9">
+        <v>0.08254256173272539</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.1678306454838297</v>
+        <v>0.1491285742838097</v>
       </c>
       <c r="B10">
-        <v>-0.2364956450038418</v>
+        <v>-0.2449972605778508</v>
       </c>
       <c r="C10">
-        <v>0.1664641305650976</v>
+        <v>0.1748824064642598</v>
       </c>
       <c r="D10">
-        <v>0.226973298262108</v>
+        <v>0.2244150345830125</v>
       </c>
       <c r="E10">
-        <v>-0.034374954096852</v>
+        <v>-0.03290908989607596</v>
       </c>
       <c r="F10">
-        <v>0.07706042505883423</v>
+        <v>0.06650251466758206</v>
       </c>
       <c r="G10">
-        <v>-0.1344548623094484</v>
+        <v>-0.1341494101292557</v>
       </c>
       <c r="H10">
-        <v>-0.05523225291946129</v>
+        <v>-0.0658935659282681</v>
       </c>
       <c r="I10">
         <v>1</v>
       </c>
       <c r="J10">
-        <v>-0.04414643810173281</v>
+        <v>-0.06935303874494579</v>
       </c>
       <c r="K10">
-        <v>-0.04103752517901923</v>
+        <v>-0.02535636446703868</v>
       </c>
       <c r="L10">
-        <v>0.1338862850947209</v>
+        <v>0.1212423803369145</v>
       </c>
       <c r="M10">
-        <v>0.1393681670990152</v>
+        <v>0.1296001751438171</v>
       </c>
       <c r="N10">
-        <v>0.2633722956319595</v>
+        <v>0.2816915902026271</v>
       </c>
       <c r="O10">
-        <v>0.1170922415368219</v>
+        <v>0.1321076805451977</v>
+      </c>
+      <c r="P10">
+        <v>0.03715510797485</v>
+      </c>
+      <c r="Q10">
+        <v>-0.2325586498729397</v>
+      </c>
+      <c r="R10">
+        <v>-0.07720896726059799</v>
+      </c>
+      <c r="S10">
+        <v>0.04891395750278285</v>
+      </c>
+      <c r="T10">
+        <v>0.00410512247108909</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.2054810311219833</v>
+        <v>0.2227186264875546</v>
       </c>
       <c r="B11">
-        <v>0.1601874074349052</v>
+        <v>0.1732248620886273</v>
       </c>
       <c r="C11">
-        <v>0.1005480868004269</v>
+        <v>0.08365565873081771</v>
       </c>
       <c r="D11">
-        <v>0.2814636725025564</v>
+        <v>0.2746088583062065</v>
       </c>
       <c r="E11">
-        <v>-0.1131078795232538</v>
+        <v>-0.1123713039747314</v>
       </c>
       <c r="F11">
-        <v>0.289818636903774</v>
+        <v>0.2973247065830599</v>
       </c>
       <c r="G11">
-        <v>-0.06598409415717404</v>
+        <v>-0.06337668668375511</v>
       </c>
       <c r="H11">
-        <v>0.1368641045250882</v>
+        <v>0.1498188364147499</v>
       </c>
       <c r="I11">
-        <v>-0.04414643810173281</v>
+        <v>-0.06935303874494579</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
       <c r="K11">
-        <v>0.261913300966114</v>
+        <v>0.2342504027298693</v>
       </c>
       <c r="L11">
-        <v>0.3651869636073108</v>
+        <v>0.3699083609243151</v>
       </c>
       <c r="M11">
-        <v>0.1675637305884676</v>
+        <v>0.1756518661803141</v>
       </c>
       <c r="N11">
-        <v>-0.1634279587686666</v>
+        <v>-0.1934034244023699</v>
       </c>
       <c r="O11">
-        <v>0.1369700192073663</v>
+        <v>0.1090607592678896</v>
+      </c>
+      <c r="P11">
+        <v>0.7427022584990643</v>
+      </c>
+      <c r="Q11">
+        <v>0.7086827303274263</v>
+      </c>
+      <c r="R11">
+        <v>0.8008673726767011</v>
+      </c>
+      <c r="S11">
+        <v>0.7533179585424105</v>
+      </c>
+      <c r="T11">
+        <v>0.5344614134024287</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>-0.192922253287266</v>
+        <v>-0.2032438124394959</v>
       </c>
       <c r="B12">
-        <v>0.2200661426643098</v>
+        <v>0.2085662646529877</v>
       </c>
       <c r="C12">
-        <v>0.104015465035635</v>
+        <v>0.1114677623722407</v>
       </c>
       <c r="D12">
-        <v>0.07951076396055393</v>
+        <v>0.07892171432252326</v>
       </c>
       <c r="E12">
-        <v>0.08322271371806197</v>
+        <v>0.08361725227997958</v>
       </c>
       <c r="F12">
-        <v>0.1236167160637273</v>
+        <v>0.1147600560033856</v>
       </c>
       <c r="G12">
-        <v>-0.06684782481868229</v>
+        <v>-0.06721692931158098</v>
       </c>
       <c r="H12">
-        <v>0.05838872468510031</v>
+        <v>0.04873352411747953</v>
       </c>
       <c r="I12">
-        <v>-0.04103752517901923</v>
+        <v>-0.02535636446703868</v>
       </c>
       <c r="J12">
-        <v>0.261913300966114</v>
+        <v>0.2342504027298693</v>
       </c>
       <c r="K12">
         <v>1</v>
       </c>
       <c r="L12">
-        <v>-0.1372142568347015</v>
+        <v>-0.1439789460352018</v>
       </c>
       <c r="M12">
-        <v>-0.1056663728940853</v>
+        <v>-0.1114072565056256</v>
       </c>
       <c r="N12">
-        <v>0.01866841278873931</v>
+        <v>0.03851188380883332</v>
       </c>
       <c r="O12">
-        <v>0.3113381224233299</v>
+        <v>0.3206301184587697</v>
+      </c>
+      <c r="P12">
+        <v>0.02897031277824099</v>
+      </c>
+      <c r="Q12">
+        <v>0.1861663103525017</v>
+      </c>
+      <c r="R12">
+        <v>0.3762736654853083</v>
+      </c>
+      <c r="S12">
+        <v>0.1649622044265479</v>
+      </c>
+      <c r="T12">
+        <v>0.07207535813089404</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.1635289584750014</v>
+        <v>0.1703700458011537</v>
       </c>
       <c r="B13">
-        <v>-0.01436676818842181</v>
+        <v>-0.009559106541230319</v>
       </c>
       <c r="C13">
-        <v>0.1254570167154984</v>
+        <v>0.1182614533242573</v>
       </c>
       <c r="D13">
-        <v>0.1972983585352703</v>
+        <v>0.200958966353168</v>
       </c>
       <c r="E13">
-        <v>-0.2609841784803624</v>
+        <v>-0.2611696373840359</v>
       </c>
       <c r="F13">
-        <v>0.1915668870945708</v>
+        <v>0.1905800200173855</v>
       </c>
       <c r="G13">
-        <v>-0.08937910091710877</v>
+        <v>-0.08827536701546351</v>
       </c>
       <c r="H13">
-        <v>0.04622065974247986</v>
+        <v>0.05215584806950567</v>
       </c>
       <c r="I13">
-        <v>0.1338862850947209</v>
+        <v>0.1212423803369145</v>
       </c>
       <c r="J13">
-        <v>0.3651869636073108</v>
+        <v>0.3699083609243151</v>
       </c>
       <c r="K13">
-        <v>-0.1372142568347015</v>
+        <v>-0.1439789460352018</v>
       </c>
       <c r="L13">
         <v>1</v>
       </c>
       <c r="M13">
-        <v>0.05462790571769856</v>
+        <v>0.0587940521161746</v>
       </c>
       <c r="N13">
-        <v>-0.1519860028604662</v>
+        <v>-0.1613313806446081</v>
       </c>
       <c r="O13">
-        <v>0.1458538825640354</v>
+        <v>0.1359587015410906</v>
+      </c>
+      <c r="P13">
+        <v>0.3819825739023092</v>
+      </c>
+      <c r="Q13">
+        <v>0.3228703823987106</v>
+      </c>
+      <c r="R13">
+        <v>0.2495602349137783</v>
+      </c>
+      <c r="S13">
+        <v>0.2006616528503797</v>
+      </c>
+      <c r="T13">
+        <v>0.09058943171973581</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.2462195022844721</v>
+        <v>0.2510782525818244</v>
       </c>
       <c r="B14">
-        <v>-0.03598643687849504</v>
+        <v>-0.03070042189020344</v>
       </c>
       <c r="C14">
-        <v>0.06607312685521408</v>
+        <v>0.06119142843282951</v>
       </c>
       <c r="D14">
-        <v>0.1556907547687171</v>
+        <v>0.1550320234728836</v>
       </c>
       <c r="E14">
-        <v>0.06983794450422055</v>
+        <v>0.06920663782528157</v>
       </c>
       <c r="F14">
-        <v>-0.01490985285469092</v>
+        <v>-0.01066490304663156</v>
       </c>
       <c r="G14">
-        <v>-0.08907985414498863</v>
+        <v>-0.08849569695377277</v>
       </c>
       <c r="H14">
-        <v>0.1048961927547674</v>
+        <v>0.1093103177022212</v>
       </c>
       <c r="I14">
-        <v>0.1393681670990152</v>
+        <v>0.1296001751438171</v>
       </c>
       <c r="J14">
-        <v>0.1675637305884676</v>
+        <v>0.1756518661803141</v>
       </c>
       <c r="K14">
-        <v>-0.1056663728940853</v>
+        <v>-0.1114072565056256</v>
       </c>
       <c r="L14">
-        <v>0.05462790571769856</v>
+        <v>0.0587940521161746</v>
       </c>
       <c r="M14">
         <v>1</v>
       </c>
       <c r="N14">
-        <v>-0.3192323492067725</v>
+        <v>-0.324187818025887</v>
       </c>
       <c r="O14">
-        <v>-0.1024614866691264</v>
+        <v>-0.1089006805710941</v>
+      </c>
+      <c r="P14">
+        <v>0.06032133651465237</v>
+      </c>
+      <c r="Q14">
+        <v>-0.01675167229686399</v>
+      </c>
+      <c r="R14">
+        <v>0.1601228270778295</v>
+      </c>
+      <c r="S14">
+        <v>0.2445051662927571</v>
+      </c>
+      <c r="T14">
+        <v>0.289440474142387</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.06776122405072027</v>
+        <v>0.04459276354807663</v>
       </c>
       <c r="B15">
-        <v>-0.1873545299721046</v>
+        <v>-0.199454559182896</v>
       </c>
       <c r="C15">
-        <v>0.07996995828609169</v>
+        <v>0.09243126180872226</v>
       </c>
       <c r="D15">
-        <v>0.08808353091238505</v>
+        <v>0.08754628572900472</v>
       </c>
       <c r="E15">
-        <v>0.0005645537134997134</v>
+        <v>0.001843250891151417</v>
       </c>
       <c r="F15">
-        <v>-0.06684242044665795</v>
+        <v>-0.07914808429291659</v>
       </c>
       <c r="G15">
-        <v>-0.05106108334772153</v>
+        <v>-0.05147795912522143</v>
       </c>
       <c r="H15">
-        <v>-0.05160104124978684</v>
+        <v>-0.06585482154983935</v>
       </c>
       <c r="I15">
-        <v>0.2633722956319595</v>
+        <v>0.2816915902026271</v>
       </c>
       <c r="J15">
-        <v>-0.1634279587686666</v>
+        <v>-0.1934034244023699</v>
       </c>
       <c r="K15">
-        <v>0.01866841278873931</v>
+        <v>0.03851188380883332</v>
       </c>
       <c r="L15">
-        <v>-0.1519860028604662</v>
+        <v>-0.1613313806446081</v>
       </c>
       <c r="M15">
-        <v>-0.3192323492067725</v>
+        <v>-0.324187818025887</v>
       </c>
       <c r="N15">
         <v>1</v>
       </c>
       <c r="O15">
-        <v>-0.03707404662514384</v>
+        <v>-0.01281797961002631</v>
+      </c>
+      <c r="P15">
+        <v>-0.0393440237721301</v>
+      </c>
+      <c r="Q15">
+        <v>-0.2331856153525731</v>
+      </c>
+      <c r="R15">
+        <v>-0.1235541241984258</v>
+      </c>
+      <c r="S15">
+        <v>-0.1192962621798739</v>
+      </c>
+      <c r="T15">
+        <v>-0.2309443669425541</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>-0.1278059168004523</v>
+        <v>-0.1404150485086712</v>
       </c>
       <c r="B16">
-        <v>0.2605993605348391</v>
+        <v>0.2464520058367095</v>
       </c>
       <c r="C16">
-        <v>0.0381212233398639</v>
+        <v>0.04715800174151601</v>
       </c>
       <c r="D16">
-        <v>0.1086231381843897</v>
+        <v>0.109024750750756</v>
       </c>
       <c r="E16">
-        <v>0.01551564781335734</v>
+        <v>0.01609515334306257</v>
       </c>
       <c r="F16">
-        <v>0.05961009914521846</v>
+        <v>0.04908496577092072</v>
       </c>
       <c r="G16">
-        <v>-0.1290678786495238</v>
+        <v>-0.1289103385701811</v>
       </c>
       <c r="H16">
-        <v>-0.001419502472943161</v>
+        <v>-0.01171596336165348</v>
       </c>
       <c r="I16">
-        <v>0.1170922415368219</v>
+        <v>0.1321076805451977</v>
       </c>
       <c r="J16">
-        <v>0.1369700192073663</v>
+        <v>0.1090607592678896</v>
       </c>
       <c r="K16">
-        <v>0.3113381224233299</v>
+        <v>0.3206301184587697</v>
       </c>
       <c r="L16">
-        <v>0.1458538825640354</v>
+        <v>0.1359587015410906</v>
       </c>
       <c r="M16">
-        <v>-0.1024614866691264</v>
+        <v>-0.1089006805710941</v>
       </c>
       <c r="N16">
-        <v>-0.03707404662514384</v>
+        <v>-0.01281797961002631</v>
       </c>
       <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>0.09093988802607726</v>
+      </c>
+      <c r="Q16">
+        <v>0.04975295280324753</v>
+      </c>
+      <c r="R16">
+        <v>0.09078041233260566</v>
+      </c>
+      <c r="S16">
+        <v>0.096129303699355</v>
+      </c>
+      <c r="T16">
+        <v>0.06515766434046262</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.1498514333392476</v>
+      </c>
+      <c r="B17">
+        <v>0.1085776736285352</v>
+      </c>
+      <c r="C17">
+        <v>-0.04094400070885888</v>
+      </c>
+      <c r="D17">
+        <v>0.1650741730086829</v>
+      </c>
+      <c r="E17">
+        <v>-0.1055307157996861</v>
+      </c>
+      <c r="F17">
+        <v>0.07933358605274295</v>
+      </c>
+      <c r="G17">
+        <v>0.04178203312533061</v>
+      </c>
+      <c r="H17">
+        <v>0.07317528681095627</v>
+      </c>
+      <c r="I17">
+        <v>0.03715510797485</v>
+      </c>
+      <c r="J17">
+        <v>0.7427022584990643</v>
+      </c>
+      <c r="K17">
+        <v>0.02897031277824099</v>
+      </c>
+      <c r="L17">
+        <v>0.3819825739023092</v>
+      </c>
+      <c r="M17">
+        <v>0.06032133651465237</v>
+      </c>
+      <c r="N17">
+        <v>-0.0393440237721301</v>
+      </c>
+      <c r="O17">
+        <v>0.09093988802607726</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>0.3506096651453878</v>
+      </c>
+      <c r="R17">
+        <v>0.5089196904640702</v>
+      </c>
+      <c r="S17">
+        <v>0.3838984230995432</v>
+      </c>
+      <c r="T17">
+        <v>0.3175690800910856</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.07726138752518816</v>
+      </c>
+      <c r="B18">
+        <v>0.2028890976282736</v>
+      </c>
+      <c r="C18">
+        <v>0.02203706588251925</v>
+      </c>
+      <c r="D18">
+        <v>0.1505053023167987</v>
+      </c>
+      <c r="E18">
+        <v>-0.2589518106208061</v>
+      </c>
+      <c r="F18">
+        <v>0.4873320020387907</v>
+      </c>
+      <c r="G18">
+        <v>-0.08782373275430254</v>
+      </c>
+      <c r="H18">
+        <v>0.1158528245081843</v>
+      </c>
+      <c r="I18">
+        <v>-0.2325586498729397</v>
+      </c>
+      <c r="J18">
+        <v>0.7086827303274263</v>
+      </c>
+      <c r="K18">
+        <v>0.1861663103525017</v>
+      </c>
+      <c r="L18">
+        <v>0.3228703823987106</v>
+      </c>
+      <c r="M18">
+        <v>-0.01675167229686399</v>
+      </c>
+      <c r="N18">
+        <v>-0.2331856153525731</v>
+      </c>
+      <c r="O18">
+        <v>0.04975295280324753</v>
+      </c>
+      <c r="P18">
+        <v>0.3506096651453878</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>0.4550470216430856</v>
+      </c>
+      <c r="S18">
+        <v>0.3576015818398858</v>
+      </c>
+      <c r="T18">
+        <v>0.2418360432425313</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.1144527085473046</v>
+      </c>
+      <c r="B19">
+        <v>0.1367630776388218</v>
+      </c>
+      <c r="C19">
+        <v>0.09100976823142341</v>
+      </c>
+      <c r="D19">
+        <v>0.1742055213462483</v>
+      </c>
+      <c r="E19">
+        <v>0.008152773604969592</v>
+      </c>
+      <c r="F19">
+        <v>0.2129724037674157</v>
+      </c>
+      <c r="G19">
+        <v>0.004570821820959719</v>
+      </c>
+      <c r="H19">
+        <v>0.137555541604289</v>
+      </c>
+      <c r="I19">
+        <v>-0.07720896726059799</v>
+      </c>
+      <c r="J19">
+        <v>0.8008673726767011</v>
+      </c>
+      <c r="K19">
+        <v>0.3762736654853083</v>
+      </c>
+      <c r="L19">
+        <v>0.2495602349137783</v>
+      </c>
+      <c r="M19">
+        <v>0.1601228270778295</v>
+      </c>
+      <c r="N19">
+        <v>-0.1235541241984258</v>
+      </c>
+      <c r="O19">
+        <v>0.09078041233260566</v>
+      </c>
+      <c r="P19">
+        <v>0.5089196904640702</v>
+      </c>
+      <c r="Q19">
+        <v>0.4550470216430856</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>0.549977768363206</v>
+      </c>
+      <c r="T19">
+        <v>0.3081655315541897</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.2637355905648565</v>
+      </c>
+      <c r="B20">
+        <v>0.05484384196750863</v>
+      </c>
+      <c r="C20">
+        <v>0.1689101999126812</v>
+      </c>
+      <c r="D20">
+        <v>0.3161345848856572</v>
+      </c>
+      <c r="E20">
+        <v>-0.003206281458413307</v>
+      </c>
+      <c r="F20">
+        <v>0.1375954870889755</v>
+      </c>
+      <c r="G20">
+        <v>-0.1043179236807127</v>
+      </c>
+      <c r="H20">
+        <v>0.1260738839238227</v>
+      </c>
+      <c r="I20">
+        <v>0.04891395750278285</v>
+      </c>
+      <c r="J20">
+        <v>0.7533179585424105</v>
+      </c>
+      <c r="K20">
+        <v>0.1649622044265479</v>
+      </c>
+      <c r="L20">
+        <v>0.2006616528503797</v>
+      </c>
+      <c r="M20">
+        <v>0.2445051662927571</v>
+      </c>
+      <c r="N20">
+        <v>-0.1192962621798739</v>
+      </c>
+      <c r="O20">
+        <v>0.096129303699355</v>
+      </c>
+      <c r="P20">
+        <v>0.3838984230995432</v>
+      </c>
+      <c r="Q20">
+        <v>0.3576015818398858</v>
+      </c>
+      <c r="R20">
+        <v>0.549977768363206</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>0.3991496696224448</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.2538913410223593</v>
+      </c>
+      <c r="B21">
+        <v>0.1124389432384647</v>
+      </c>
+      <c r="C21">
+        <v>0.09047973358408784</v>
+      </c>
+      <c r="D21">
+        <v>0.198409316562796</v>
+      </c>
+      <c r="E21">
+        <v>0.02970359868433875</v>
+      </c>
+      <c r="F21">
+        <v>0.07858683641614395</v>
+      </c>
+      <c r="G21">
+        <v>-0.1225439494279437</v>
+      </c>
+      <c r="H21">
+        <v>0.08254256173272539</v>
+      </c>
+      <c r="I21">
+        <v>0.00410512247108909</v>
+      </c>
+      <c r="J21">
+        <v>0.5344614134024287</v>
+      </c>
+      <c r="K21">
+        <v>0.07207535813089404</v>
+      </c>
+      <c r="L21">
+        <v>0.09058943171973581</v>
+      </c>
+      <c r="M21">
+        <v>0.289440474142387</v>
+      </c>
+      <c r="N21">
+        <v>-0.2309443669425541</v>
+      </c>
+      <c r="O21">
+        <v>0.06515766434046262</v>
+      </c>
+      <c r="P21">
+        <v>0.3175690800910856</v>
+      </c>
+      <c r="Q21">
+        <v>0.2418360432425313</v>
+      </c>
+      <c r="R21">
+        <v>0.3081655315541897</v>
+      </c>
+      <c r="S21">
+        <v>0.3991496696224448</v>
+      </c>
+      <c r="T21">
         <v>1</v>
       </c>
     </row>
